--- a/Outputs/PtX_demand_EU27.xlsx
+++ b/Outputs/PtX_demand_EU27.xlsx
@@ -503,11 +503,19 @@
       <c r="E2" t="n">
         <v>0.04716776709385711</v>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
+      <c r="F2" t="n">
+        <v>0.5717885897442716</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.211933108459677</v>
+      </c>
       <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="I2" t="n">
+        <v>0.2213298425697075</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.0703367467137985</v>
+      </c>
       <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
@@ -730,16 +738,18 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Fossil Residuals</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>2030</v>
       </c>
-      <c r="C12" t="inlineStr"/>
+      <c r="C12" t="n">
+        <v>0.4290842433362655</v>
+      </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
-        <v>0.191636547641208</v>
+        <v>0.5108014857278653</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
@@ -751,18 +761,16 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Fossil Rest</t>
+          <t>Biomass [Solid]</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>2030</v>
       </c>
-      <c r="C13" t="n">
-        <v>0.4290842433362655</v>
-      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
-        <v>0.5108014857278653</v>
+        <v>0.191636547641208</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
@@ -805,25 +813,25 @@
         <v>0.8191346513205151</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8873450719697544</v>
+        <v>0.8873450719697543</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8063615210993599</v>
+        <v>0.80636152109936</v>
       </c>
       <c r="F15" t="n">
-        <v>5.265668285695435</v>
+        <v>5.837456875439707</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0420941824597003</v>
+        <v>0.2540272909193773</v>
       </c>
       <c r="H15" t="n">
         <v>1.517999109009769</v>
       </c>
       <c r="I15" t="n">
-        <v>3.745281158207061</v>
+        <v>3.966611000776768</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0547425698370636</v>
+        <v>0.1250793165508621</v>
       </c>
       <c r="K15" t="n">
         <v>2.047540194129764</v>
@@ -847,11 +855,19 @@
       <c r="E16" t="n">
         <v>0.04267178352514552</v>
       </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
+      <c r="F16" t="n">
+        <v>1.62173211576467</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.248723050765084</v>
+      </c>
       <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+      <c r="I16" t="n">
+        <v>0.7791834859896341</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.06936837763463739</v>
+      </c>
       <c r="K16" t="inlineStr"/>
     </row>
     <row r="17">
@@ -1078,16 +1094,20 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Fossil Residuals</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>2040</v>
       </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
+      <c r="C26" t="n">
+        <v>0.2501740811965058</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1.309672370553017e-17</v>
+      </c>
       <c r="E26" t="n">
-        <v>0.1801364487631514</v>
+        <v>0.2734504175289143</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
@@ -1099,20 +1119,16 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Fossil Rest</t>
+          <t>Biomass [Solid]</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>2040</v>
       </c>
-      <c r="C27" t="n">
-        <v>0.2501740811965058</v>
-      </c>
-      <c r="D27" t="n">
-        <v>1.309672370553017e-17</v>
-      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="n">
-        <v>0.2734504175289143</v>
+        <v>0.1801364487631514</v>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
@@ -1158,22 +1174,22 @@
         <v>0.8953183885759565</v>
       </c>
       <c r="E29" t="n">
-        <v>0.6785589281698209</v>
+        <v>0.6785589281698208</v>
       </c>
       <c r="F29" t="n">
-        <v>1.68303867889381</v>
+        <v>3.30477079465848</v>
       </c>
       <c r="G29" t="n">
-        <v>0.048158936132442</v>
+        <v>0.296881986897526</v>
       </c>
       <c r="H29" t="n">
         <v>1.482355615115942</v>
       </c>
       <c r="I29" t="n">
-        <v>1.822182342758817</v>
+        <v>2.601365828748451</v>
       </c>
       <c r="J29" t="n">
-        <v>0.0511204913562362</v>
+        <v>0.1204888689908736</v>
       </c>
       <c r="K29" t="n">
         <v>2.009473541668771</v>
@@ -1197,11 +1213,19 @@
       <c r="E30" t="n">
         <v>0.03819360943847092</v>
       </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
+      <c r="F30" t="n">
+        <v>1.886339370312639</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.279314532345502</v>
+      </c>
       <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+      <c r="I30" t="n">
+        <v>1.170531877660387</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.07084759313032429</v>
+      </c>
       <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
@@ -1440,7 +1464,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Fossil Residuals</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -1448,9 +1472,7 @@
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
-      <c r="E40" t="n">
-        <v>0.1561590393106004</v>
-      </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
@@ -1461,7 +1483,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Fossil Rest</t>
+          <t>Biomass [Solid]</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -1469,7 +1491,9 @@
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
+      <c r="E41" t="n">
+        <v>0.1561590393106004</v>
+      </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
@@ -1514,22 +1538,22 @@
         <v>0.903260121294739</v>
       </c>
       <c r="E43" t="n">
-        <v>0.5519705072332419</v>
+        <v>0.5519705072332418</v>
       </c>
       <c r="F43" t="n">
-        <v>0.3317579802912112</v>
+        <v>2.218097350603851</v>
       </c>
       <c r="G43" t="n">
-        <v>0.05098701418162325</v>
+        <v>0.3303015465271253</v>
       </c>
       <c r="H43" t="n">
         <v>1.400830226972303</v>
       </c>
       <c r="I43" t="n">
-        <v>0.3823590808493458</v>
+        <v>1.552890958509733</v>
       </c>
       <c r="J43" t="n">
-        <v>0.04801321083678314</v>
+        <v>0.1188608039671074</v>
       </c>
       <c r="K43" t="n">
         <v>1.968588884318871</v>
